--- a/www/download/COUNTRY.ROW.rpA2.xlsx
+++ b/www/download/COUNTRY.ROW.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>Resto do mundo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.289</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>856.406</t>
+          <t>-0.0953158457410942</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>877.09</t>
+          <t>-0.05579560636414</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>896.559</t>
+          <t>-0.0678401617870862</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>911.591</t>
+          <t>-0.093491066349475</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>926.097</t>
+          <t>-0.133698451930783</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>955.308</t>
+          <t>-0.133760894173209</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>983.772</t>
+          <t>-0.0966439641797612</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>998.606</t>
+          <t>-0.10096531324653</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1035.462</t>
+          <t>-0.0316043899825678</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1066.542</t>
+          <t>0.0129663142355403</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1095.297</t>
+          <t>0.00678465647836712</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1124.55</t>
+          <t>0.0228873511979857</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1146.413</t>
+          <t>0.126367761104867</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1174.341</t>
+          <t>0.19470859076616</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1192.928</t>
+          <t>0.182016776891606</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>370.557</t>
+          <t>0.0873712495192687</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>379.509</t>
+          <t>0.133122592703104</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>390.19</t>
+          <t>0.107644655760385</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>395.691</t>
+          <t>0.0955403589012565</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>400.131</t>
+          <t>0.0839813117101873</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>413.204</t>
+          <t>0.054014386351273</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>426.421</t>
+          <t>0.0557907000693965</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>433.848</t>
+          <t>0.0754881458769412</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>450.765</t>
+          <t>0.150421125590984</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>467.784</t>
+          <t>0.190890376326781</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>483.061</t>
+          <t>0.189503928374582</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>500.543</t>
+          <t>0.199161332794719</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>514.72</t>
+          <t>0.292339976197499</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>530.955</t>
+          <t>0.310169320915963</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>540.638</t>
+          <t>0.33774951563908</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1581950.09</t>
+          <t>0.0342487308495911</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1632216.323</t>
+          <t>0.0609949180540144</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1661461.975</t>
+          <t>0.053257702155306</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1675206.949</t>
+          <t>0.0743335660361681</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1699153.059</t>
+          <t>0.079329615577751</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1763177.932</t>
+          <t>0.0264912773599357</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1837303.246</t>
+          <t>0.0440622662134944</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1878897.895</t>
+          <t>0.0700069449478196</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1972073.419</t>
+          <t>-0.0244244648935811</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2057200.705</t>
+          <t>0.123818488674506</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2101215.075</t>
+          <t>0.0954832046374732</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2166673.727</t>
+          <t>0.0844936232762754</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2217052.892</t>
+          <t>0.0974349053840715</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2300250.74</t>
+          <t>0.0449364450116001</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2339590.627</t>
+          <t>0.134191463752858</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>684490.338</t>
+          <t>4392360070136</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>706246.059</t>
+          <t>4561341693935.22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>723082.616</t>
+          <t>4749942221021.78</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>727150.964</t>
+          <t>4839934033440.72</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>734138.16</t>
+          <t>4868931491191.25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>762635.984</t>
+          <t>5091242635044.44</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>796388.724</t>
+          <t>5333214032018.04</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>816293.521</t>
+          <t>5597698897946.12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>858497.817</t>
+          <t>5870188948961.68</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>902286.807</t>
+          <t>6182071405396.57</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>926704.183</t>
+          <t>6393496831371.4</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>964398.177</t>
+          <t>6713239614048.22</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>995418.423</t>
+          <t>6791428812880.71</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1040011.962</t>
+          <t>7005336646667.93</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1060308.098</t>
+          <t>7346722396747.9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>1412710619221.51</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>1425143912987.41</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>1498134133934.28</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>1524721597660.27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>1578145664285.07</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>1705732088568.04</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>1777652024725.55</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>1812795583981.11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1862340013147.2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>1895745656102.62</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>1975794288355</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>2054831761791.48</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>2013243835846.95</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>2100958934527.76</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>2136023513280.6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>17380843.6736083</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>17416026.508201</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>17801258.6375186</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>18826511.737941</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>19033206.2380059</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>19527523.4465163</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>20847837.7221798</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>21162629.1748837</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>20346606.8732875</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>19257628.9491272</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>17581027.6362526</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>16167365.3379799</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>14328336.5124031</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>12471294.5218392</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>13962314.72264</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>11777580.3251009</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>12138918.3362634</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>12272139.797989</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>12340563.1523873</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>12999572.2613256</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>13831668.0012158</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>13973322.968032</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>14720853.2810752</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>16636845.1978497</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>19020643.2156679</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>20792493.527963</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>22622680.9314783</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>26047193.1847039</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>29877725.0640038</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>28444713.8804135</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>35.89</t>
+          <t>19160130.5296985</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>19836491.3151498</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>20316151.9456063</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>20445905.8756702</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>21221237.8948146</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>22316756.6076057</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>22551155.4178981</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>23973800.35025</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>39.74</t>
+          <t>26917247.6147694</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>30745623.5528469</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>33821453.3239725</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>36961322.5797225</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>41917579.7971936</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>47233025.61079</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>45785146.8034092</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>0.0169303090191604</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.29</t>
+          <t>0.0557529826085998</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>0.0380841945697274</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>0.027800247784727</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>0.00835599155332378</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>-0.0167831808722732</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>-0.000275884479982613</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>0.0108222240074105</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>0.0491674526961485</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>0.111631251449643</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>0.102968674369784</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0.11086636410285</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>0.19229294174834</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>0.216041977063292</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>0.23962308245023</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>834359.584527764</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>875995.799515621</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>888232.735690991</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>817887.455920437</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>820870.645971099</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>13.96</t>
+          <t>836667.08690153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>817433.866052652</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>808667.728954467</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>900867.030276919</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>1020802.53907012</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>1174139.92751623</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>1288849.39089663</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>1462975.42687985</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>1414733.6337512</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>1300131.74826274</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3812.40255933302</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3755.22867800286</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3839.49711241964</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3853.31346500457</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3944.07618217828</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4128.06028922543</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4168.77070801842</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4178.41594911528</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4131.50799771765</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4052.60547861503</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4090.15063307741</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4105.2015010642</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3911.34100674902</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3956.94487817682</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3950.93308398205</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.656</t>
+          <t>-508429222962.798</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.752</t>
+          <t>-531585909120.083</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.776</t>
+          <t>-454589510263.338</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.711</t>
+          <t>-487339760586.412</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>-532714082033.813</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.808</t>
+          <t>-595487598032.312</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>-638280893817.358</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.777</t>
+          <t>-684976879893.024</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-789664396752.465</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.269</t>
+          <t>-874291843060.974</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.609</t>
+          <t>-883097733554.508</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.975</t>
+          <t>-902781026577.375</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>3.462</t>
+          <t>-947265862885.792</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-992334421995.914</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>-950064683055.916</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.913</t>
+          <t>-471649239554.266</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>-492281374137.553</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>-409155027729.322</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>-442032941372.223</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.973</t>
+          <t>-484884472818.285</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.051</t>
+          <t>-537753060395.376</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>-584534297687.249</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.012</t>
+          <t>-620611565454.917</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>-721459691219.782</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.581</t>
+          <t>-794174565283.008</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.963</t>
+          <t>-795790895737.91</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>-808701354620.293</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>3.944</t>
+          <t>-848066790570.599</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>4.811</t>
+          <t>-902066452502.328</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>-870752843952.194</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11.287</t>
+          <t>-36779983408.5317</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.943</t>
+          <t>-39304534982.5303</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11.946</t>
+          <t>-45434482534.0153</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11.365</t>
+          <t>-45306819214.1892</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11.408</t>
+          <t>-47829609215.528</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11.324</t>
+          <t>-57734537636.9353</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.035</t>
+          <t>-53746596130.1092</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10.701</t>
+          <t>-64365314438.1064</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>11.762</t>
+          <t>-68204705532.6823</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>13.123</t>
+          <t>-80117277777.9655</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>14.756</t>
+          <t>-87306837816.5986</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>16.116</t>
+          <t>-94079671957.082</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>18.165</t>
+          <t>-99199072315.1928</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>16.479</t>
+          <t>-90267969493.5858</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>-79311839103.7213</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.003</t>
+          <t>3876.94771276797</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.424</t>
+          <t>3964.59387717887</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.544</t>
+          <t>3985.72126749893</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6.264</t>
+          <t>3960.43653412392</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.334</t>
+          <t>3977.03284944223</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6.598</t>
+          <t>4058.77830673971</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.586</t>
+          <t>4167.62060887947</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6.544</t>
+          <t>4223.63570251274</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7.373</t>
+          <t>4334.6437217592</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>4505.0028998245</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10.019</t>
+          <t>4511.30802173813</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>11.506</t>
+          <t>4560.33026539675</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>13.579</t>
+          <t>4663.46427511771</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>16.651</t>
+          <t>4811.8110727886</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>4897.66784812043</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3876.94771276797</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3964.59387717887</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3985.72126749893</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3.221</t>
+          <t>3960.43653412392</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.257</t>
+          <t>3977.03284944222</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.398</t>
+          <t>4058.77830673971</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>4167.62060887947</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3.352</t>
+          <t>4223.63570251274</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3.736</t>
+          <t>4334.6437217592</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4.357</t>
+          <t>4505.0028998245</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4511.30802173813</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5.791</t>
+          <t>4560.33026539675</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>6.786</t>
+          <t>4663.46427511771</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>8.286</t>
+          <t>4811.8110727886</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>7.707</t>
+          <t>4897.66784812043</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>701304.802261108</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>776487.373711383</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>635985.074643795</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>643545.401190691</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>824736.144773895</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>1081819.67187864</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-9.66</t>
+          <t>1089314.484167</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-10.1</t>
+          <t>1102602.17304957</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>1308815.13215068</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1623206.21854965</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>2014786.55736804</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2317531.5351085</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>2656330.43359939</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>3336283.80342492</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>2360037.21884672</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>553809787764.195</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>595745959396.593</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>472238153133.582</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>517065761306.983</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>611760080336.919</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>736301700256.239</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>794450759477.491</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>841277290311.033</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>964384744912.828</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>1075581552283.47</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>1137093318844.96</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>1178116527652.34</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>1221953092841.09</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>1325715962023.64</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>1149048104967.7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1058937.18147773</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1116736.07292101</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>1044258.26035641</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>1011695.46046075</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>1054009.48402831</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1179943.33914034</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1176102.18515089</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1252329.84766961</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>1469427.2441954</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>1797530.83578138</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>2133448.93119307</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>2477531.07134706</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>3027613.30210319</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>3566779.2030106</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>2796920.48323512</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3320242.898</t>
+          <t>148227568472.234</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3477304.47</t>
+          <t>159926231395.916</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3573433.985</t>
+          <t>124528642972.539</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3610298.842</t>
+          <t>132294062022.563</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3683118.334</t>
+          <t>145381674716.175</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3877385.371</t>
+          <t>169821924469.045</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4099988.703</t>
+          <t>183351010608.303</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4217746.235</t>
+          <t>203111440140.096</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4488359.841</t>
+          <t>222276395750.42</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4804773.001</t>
+          <t>249146502925.273</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4941221.109</t>
+          <t>284335426396.614</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>5128321.261</t>
+          <t>312932441634.929</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>5346255.758</t>
+          <t>352143116721.469</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>5650709.423</t>
+          <t>376872202510.871</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>5842563.994</t>
+          <t>290908815488.829</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1436628.247</t>
+          <t>-357632.379216618</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1504599.937</t>
+          <t>-340248.699209626</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1555189.366</t>
+          <t>-408273.185712613</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1567109.236</t>
+          <t>-368150.059270054</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1591332.636</t>
+          <t>-229273.33925441</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1677104.478</t>
+          <t>-98123.6672616966</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1777161.598</t>
+          <t>-86787.7009838913</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1832414.064</t>
+          <t>-149727.674620044</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1953906.528</t>
+          <t>-160612.112044718</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2107370.116</t>
+          <t>-174324.617231727</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2179239.207</t>
+          <t>-118662.373825036</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2282643.488</t>
+          <t>-159999.536238555</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2400376.415</t>
+          <t>-371282.868503794</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2554854.256</t>
+          <t>-230495.399585683</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2647864.052</t>
+          <t>-436883.264388399</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4392360.07</t>
+          <t>405582219291.961</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4561341.694</t>
+          <t>435819728000.677</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4749942.221</t>
+          <t>347709510161.043</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4839934.033</t>
+          <t>384771699284.42</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4868931.491</t>
+          <t>466378405620.744</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5091242.635</t>
+          <t>566479775787.194</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5333214.032</t>
+          <t>611099748869.188</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5597698.898</t>
+          <t>638165850170.937</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5870188.949</t>
+          <t>742108349162.408</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6182071.405</t>
+          <t>826435049358.193</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>6393496.831</t>
+          <t>852757892448.347</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6713239.614</t>
+          <t>865184086017.408</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>6791428.813</t>
+          <t>869809976119.621</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>7005336.647</t>
+          <t>948843759512.769</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>7346722.397</t>
+          <t>858139289478.875</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>1693452.24787689</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19.836</t>
+          <t>1815616.36512757</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.316</t>
+          <t>1835440.60484036</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20.446</t>
+          <t>1710026.40859875</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21.221</t>
+          <t>1753515.4220765</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>22.317</t>
+          <t>1895478.1988017</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>22.551</t>
+          <t>1856320.04175743</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>23.974</t>
+          <t>1874128.27508539</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>26.917</t>
+          <t>2096782.94164291</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>30.746</t>
+          <t>2481700.42397383</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>33.821</t>
+          <t>2938719.14606415</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>36.961</t>
+          <t>3403204.25777267</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>41.918</t>
+          <t>3942426.48415527</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>47.233</t>
+          <t>4952165.09986518</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>45.785</t>
+          <t>4395050.71325839</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2699948.91</t>
+          <t>-0.0739203932753493</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2791307.87</t>
+          <t>-0.0733510692176721</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2869241.928</t>
+          <t>-0.0743544942777961</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2921245.552</t>
+          <t>-0.0719684915091149</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2982579.389</t>
+          <t>-0.0719576120389443</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3155493.385</t>
+          <t>-0.0738822163236586</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3304607.713</t>
+          <t>-0.0740785675068383</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3437206.575</t>
+          <t>-0.0755670600218539</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3628209.92</t>
+          <t>-0.0765913131631231</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3824510.969</t>
+          <t>-0.0777855322760167</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3930544.918</t>
+          <t>-0.0795722985676879</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4108929.746</t>
+          <t>-0.0799720171145983</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4220130.531</t>
+          <t>-0.0805374597281697</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4431296.103</t>
+          <t>-0.0858503760875483</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4564262.236</t>
+          <t>-0.0830100473911866</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11.778</t>
+          <t>1656099.77634291</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12.139</t>
+          <t>1752367.9646248</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12.272</t>
+          <t>1775560.24831936</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>12.341</t>
+          <t>1710628.53985104</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1729179.1735902</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>13.832</t>
+          <t>1808311.6142287</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>13.973</t>
+          <t>1805400.01718355</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14.721</t>
+          <t>1776618.243776</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>16.637</t>
+          <t>1970113.47623266</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>19.021</t>
+          <t>2268914.53320351</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>20.792</t>
+          <t>2608844.29810359</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>22.623</t>
+          <t>2975171.26753475</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>26.047</t>
+          <t>3462290.42564073</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>29.878</t>
+          <t>4230212.3731713</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>28.445</t>
+          <t>3950317.57228416</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1412710.619</t>
+          <t>1912553.25961093</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1425143.913</t>
+          <t>2024580.61430081</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1498134.134</t>
+          <t>2042561.38369465</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1524721.598</t>
+          <t>1955571.25946932</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1578145.664</t>
+          <t>1972638.68944014</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1705732.089</t>
+          <t>2051263.03792785</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1777652.025</t>
+          <t>2042383.82250289</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1812795.584</t>
+          <t>2011676.3093988</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1862340.013</t>
+          <t>2240887.68697854</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1895745.656</t>
+          <t>2581201.91080858</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1975794.288</t>
+          <t>2963357.73251987</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2054831.762</t>
+          <t>3375554.56705043</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2013243.836</t>
+          <t>3944366.02144599</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2100958.935</t>
+          <t>4810828.23995541</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2136023.513</t>
+          <t>4486795.96693829</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>11287271.9902858</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>11942508.9348878</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>11945918.5933329</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>11364521.3171774</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>11407697.1526909</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>11324336.6067459</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>11034687.812736</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>10701325.7988415</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>11762000.0633527</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>13123295.6721036</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>14755636.6807407</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>16116254.6275372</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>18165154.8461758</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>16479061.5746225</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>15662341.9588696</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>17.381</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>17.416</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.801</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>18.827</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19.033</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>19.528</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20.848</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>21.163</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>20.347</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>19.258</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>17.581</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>16.167</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>14.328</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>12.471</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>13.962</t>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1436628246559.58</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1504599936782.95</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1555189365782.58</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1567109235877.95</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1591332636125.75</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1677104478405.96</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1777161598121.12</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1832414063870.6</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1953906527647.76</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2107370116123.57</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2179239207054.3</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2282643488064.36</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2400376415498.68</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2554854256471.92</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2647864051719.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3320242898424.88</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3477304469818.57</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3573433984902.78</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3610298841574.19</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3683118333943.08</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3877385370585.73</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4099988702527.05</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4217746234901.34</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4488359841384.35</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>4804773000783.46</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>4941221109196.17</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5128321260566.66</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>5346255757578.41</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>5650709423311.55</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>5842563994054.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2699948910191.81</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2791307870267.64</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2869241927547.02</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2921245551860.68</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2982579389049.23</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3155493384624.27</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3304607712821.75</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3437206574861.71</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3628209920408.7</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3824510969299.98</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3930544918160.48</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4108929746158.27</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4220130531035.84</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4431296102744.71</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4564262236214.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>856406416.7</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>877089703.9</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>896558927.5</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>911591136.6</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>926097036</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>955308488.8</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>983772057.8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>998605592.9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1035462227</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1066541600</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1095296771</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1124550408</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1146412933</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1174341498</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1192927772</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>370556518.425133</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>379509221.724772</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>390190196.806831</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>395691036.171245</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>400130624.103076</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>413204257.946556</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>426421156.075177</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>433847564.736811</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>450765196.188898</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>467784408.353138</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>483061497.143057</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>500543459.622823</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>514719589.10591</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>530954814.689202</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>540637734.903813</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1581950090380.27</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1632216323446.71</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1661461975045.46</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1675206949481.46</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1699153059439.56</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1763177932464.47</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1837303245908.48</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1878897894530.26</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1972073419433.81</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2057200705221.21</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2101215074715.22</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2166673727183.3</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2217052892146.03</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2300250740267.96</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2339590626746.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>684490338211.679</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>706246058804.897</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>723082616373.875</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>727150963878.283</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>734138160140.059</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>762635983824.331</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>796388724368.756</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>816293521413.016</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>858497817332.735</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>902286806961.455</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>926704183455.952</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>964398176874.085</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>995418422823.631</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1040011962123.2</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1060308098055.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.228898648427933</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.231919837016752</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.233019160662987</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.235284951021892</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.240991356161571</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.247797250380012</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.249827856813299</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.256671032957441</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.249986894033455</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.274989880290778</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.282125256882255</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.287263989153529</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.289429468407217</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.297021226523762</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.306401074424642</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.453619150842876</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.458991502302581</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.463130386661843</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.465589634981445</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.471018569897122</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.471636483388593</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.473224520750676</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.47349384372661</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.460707877633889</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.472300993256089</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.470266756125835</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.469502423185547</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.466965109699573</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.464136590079048</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.463349681517467</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.317482200729191</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.309088660680667</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.30385045267517</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.299125413996663</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.287990073941307</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.280566266231395</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.276947622436025</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.269835123315949</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.289305228332656</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.252709126453133</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.24760798699191</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.243233587660924</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.24360542189321</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.23884218339719</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.230249244057891</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.35888876847864</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.361768228723269</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.363434604258784</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.366239830682011</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.37078657430088</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.375910369161607</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.380326360659847</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.389706676967636</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.397351885995968</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.41009703203073</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.417337188241025</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.422705102041738</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.428799573585419</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.438082000527252</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.449929453161122</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.481081364027288</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.482914782999773</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.484508597686212</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.484374909721412</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.485974399802187</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.48451179610014</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.4827588095723</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.478284710942443</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.475169752304089</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.468603305195726</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.464942577376845</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.461986680306437</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.457044841299505</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.451477972645133</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.444806278159611</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.160029867494072</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.155316988276958</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.152056798055004</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.149385259596577</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.143239025896933</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.139577834738253</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.136914829767853</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.132008612089921</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.127478361699943</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.121299662773544</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.11772023438213</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.115308217651824</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.114155585115076</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.110440026827615</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.105264268679266</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>6003296.72858969</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6424492.30466808</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>6543783.60858558</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6264479.68287485</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>6333545.30128171</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6598368.92172176</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6585685.88599394</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>6543553.25004621</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>7373150.32141448</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>8620444.58875593</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10018945.050815</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>11505716.776729</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>13579035.7644158</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>16651487.3993075</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>15730361.8590702</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3100061.91984787</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3310373.4744688</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3370415.8176897</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3221261.55108232</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3257066.93491647</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3398413.01767922</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3375819.90928846</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3352394.52778614</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>3736360.3239901</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4357033.25331906</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5050013.08052761</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5791309.48199016</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6786121.13592133</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>8285953.90396788</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7706866.58207004</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
